--- a/DownloadVideo/Resource/BT.xlsx
+++ b/DownloadVideo/Resource/BT.xlsx
@@ -2196,6 +2196,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>已存在</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>https://309r.0i284.net/forum.php?mod=viewthread&amp;tid=661711&amp;extra=page%3D4%26filter%3Dtypeid%26typeid%3D654</t>
